--- a/2022 data/excel_outputs/161_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/161_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="476">
   <si>
     <t>AC 161 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -883,7 +949,7 @@
     <t>J.H.S.JANIGAW R.N. 1</t>
   </si>
   <si>
-    <t>J.H.S.JANIGAW R.N. ■</t>
+    <t>J.H.S. PAVAYAN</t>
   </si>
   <si>
     <t>P.P. JANIGAUN</t>
@@ -1012,9 +1078,6 @@
     <t>P.P. PAVAYAN</t>
   </si>
   <si>
-    <t>J.H.S. PAVAYAN</t>
-  </si>
-  <si>
     <t>P.P. RAIKBAR KHERA</t>
   </si>
   <si>
@@ -1246,7 +1309,7 @@
     <t>PANCHYATGHAR BHATPUR ROOM NO 02</t>
   </si>
   <si>
-    <t>P.P. KATKAKALAN MA0 BHATPUR R.N. ■■</t>
+    <t>PANCHYATGHAR BHATPUR ROOM ROOM NO. 408</t>
   </si>
   <si>
     <t>P.P. KATKAKALAN MA0 BHATPUR ROOM NO. 2</t>
@@ -1385,8 +1448,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1402,7 +1473,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1410,12 +1481,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1714,79 +1803,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="E2" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="F2" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="G2" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="H2" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="I2" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="J2" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="K2" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="L2" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="M2" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="N2" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="O2" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="P2" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="Q2" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="R2" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="S2" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="T2" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="U2" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="V2" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="W2" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1794,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1865,7 +2020,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1936,7 +2091,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -2007,7 +2162,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2078,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2149,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2220,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -2291,7 +2446,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -2362,7 +2517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2433,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2504,7 +2659,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -2575,7 +2730,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2646,7 +2801,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2717,7 +2872,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2788,7 +2943,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2859,7 +3014,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -2930,7 +3085,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -3001,7 +3156,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -3072,7 +3227,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -3143,7 +3298,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -3214,7 +3369,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -3285,7 +3440,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -3356,7 +3511,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -3427,7 +3582,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -3498,7 +3653,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -3569,7 +3724,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -3640,7 +3795,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -3711,7 +3866,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -3782,7 +3937,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -3853,7 +4008,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -3924,7 +4079,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -3995,7 +4150,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -4066,7 +4221,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -4137,7 +4292,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -4208,7 +4363,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -4279,7 +4434,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -4350,7 +4505,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -4421,7 +4576,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -4492,7 +4647,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -4563,7 +4718,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -4634,7 +4789,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -4705,7 +4860,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -4776,7 +4931,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -4847,7 +5002,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -4918,7 +5073,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -4989,7 +5144,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -5060,7 +5215,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -5131,7 +5286,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5202,7 +5357,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5273,7 +5428,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5344,7 +5499,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5415,7 +5570,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5486,7 +5641,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -5557,7 +5712,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -5628,7 +5783,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -5699,7 +5854,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -5770,7 +5925,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -5841,7 +5996,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -5912,7 +6067,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -5983,7 +6138,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -6054,7 +6209,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -6125,7 +6280,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -6196,7 +6351,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -6267,7 +6422,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6338,7 +6493,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6409,7 +6564,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6480,7 +6635,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6551,7 +6706,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -6622,7 +6777,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -6693,7 +6848,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -6764,7 +6919,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6835,7 +6990,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6906,7 +7061,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6977,7 +7132,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -7048,7 +7203,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -7119,7 +7274,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -7190,7 +7345,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -7261,7 +7416,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -7332,7 +7487,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -7403,7 +7558,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -7474,7 +7629,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -7545,7 +7700,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -7616,7 +7771,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -7687,7 +7842,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -7758,7 +7913,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -7829,7 +7984,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -7900,7 +8055,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -7971,7 +8126,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -8042,7 +8197,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -8113,7 +8268,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -8184,7 +8339,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -8255,7 +8410,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8326,7 +8481,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -8397,7 +8552,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -8468,7 +8623,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -8539,7 +8694,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -8610,7 +8765,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -8681,7 +8836,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -8752,7 +8907,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -8823,7 +8978,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -8894,7 +9049,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -8965,7 +9120,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -9036,7 +9191,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -9107,7 +9262,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -9178,7 +9333,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -9249,7 +9404,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -9320,7 +9475,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -9391,7 +9546,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -9462,7 +9617,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -9533,7 +9688,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -9604,7 +9759,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -9675,7 +9830,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -9746,7 +9901,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -9817,7 +9972,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -9888,7 +10043,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -9959,7 +10114,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -10030,7 +10185,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -10101,7 +10256,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -10172,7 +10327,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -10243,7 +10398,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -10314,7 +10469,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -10385,7 +10540,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -10456,7 +10611,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -10527,7 +10682,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -10598,7 +10753,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -10669,7 +10824,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -10740,7 +10895,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -10811,7 +10966,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -10882,7 +11037,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -10953,7 +11108,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -11024,7 +11179,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -11095,7 +11250,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -11166,7 +11321,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -11237,7 +11392,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -11308,7 +11463,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -11379,7 +11534,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -11450,7 +11605,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -11521,7 +11676,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>0</v>
@@ -11592,7 +11747,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -11663,7 +11818,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -11734,7 +11889,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -11805,7 +11960,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -11876,7 +12031,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -11947,7 +12102,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -12018,7 +12173,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -12089,7 +12244,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -12160,7 +12315,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -12231,7 +12386,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -12302,7 +12457,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -12373,7 +12528,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -12444,7 +12599,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -12515,7 +12670,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -12586,7 +12741,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -12657,7 +12812,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -12728,7 +12883,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -12799,7 +12954,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -12870,7 +13025,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -12941,7 +13096,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -13012,7 +13167,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -13083,7 +13238,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -13154,7 +13309,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -13225,7 +13380,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -13296,7 +13451,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -13367,7 +13522,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -13438,7 +13593,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -13509,7 +13664,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -13580,7 +13735,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -13651,7 +13806,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -13722,7 +13877,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -13793,7 +13948,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>0</v>
@@ -13864,7 +14019,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -13935,7 +14090,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -14006,7 +14161,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -14077,7 +14232,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -14148,7 +14303,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -14219,7 +14374,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -14290,7 +14445,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -14361,7 +14516,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -14432,7 +14587,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -14503,7 +14658,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -14574,7 +14729,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -14645,7 +14800,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -14716,7 +14871,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -14787,7 +14942,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -14858,7 +15013,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -14929,7 +15084,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -15000,7 +15155,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -15071,7 +15226,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -15142,7 +15297,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -15213,7 +15368,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -15284,7 +15439,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -15355,7 +15510,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -15426,7 +15581,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -15497,7 +15652,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -15568,7 +15723,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -15639,7 +15794,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -15710,7 +15865,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -15781,7 +15936,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -15852,7 +16007,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -15923,7 +16078,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -15994,7 +16149,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -16065,7 +16220,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -16136,7 +16291,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -16207,7 +16362,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -16278,7 +16433,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -16349,7 +16504,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -16420,7 +16575,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -16491,7 +16646,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -16562,7 +16717,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -16633,7 +16788,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -16704,7 +16859,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -16775,7 +16930,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -16846,7 +17001,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -16917,7 +17072,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -16988,7 +17143,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -17059,7 +17214,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -17130,7 +17285,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -17201,7 +17356,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -17272,7 +17427,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -17343,7 +17498,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -17414,7 +17569,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -17485,7 +17640,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -17556,7 +17711,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -17627,7 +17782,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -17698,7 +17853,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -17769,7 +17924,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -17840,7 +17995,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -17911,7 +18066,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -17982,7 +18137,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -18053,7 +18208,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -18124,7 +18279,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -18195,7 +18350,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -18266,7 +18421,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -18337,7 +18492,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -18408,7 +18563,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -18479,7 +18634,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -18550,7 +18705,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -18621,7 +18776,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -18692,7 +18847,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -18763,7 +18918,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -18834,7 +18989,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -18905,7 +19060,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -18976,7 +19131,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -19047,7 +19202,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -19118,7 +19273,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -19189,7 +19344,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -19260,7 +19415,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -19331,7 +19486,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -19402,7 +19557,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -19473,7 +19628,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -19544,7 +19699,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -19615,7 +19770,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -19686,7 +19841,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -19757,7 +19912,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -19828,7 +19983,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>0</v>
@@ -19899,7 +20054,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -19970,7 +20125,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>0</v>
@@ -20041,7 +20196,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>0</v>
@@ -20112,7 +20267,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -20183,7 +20338,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -20254,7 +20409,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -20325,7 +20480,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -20396,7 +20551,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -20467,7 +20622,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -20538,7 +20693,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -20609,7 +20764,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -20680,7 +20835,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -20751,7 +20906,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -20822,7 +20977,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -20893,7 +21048,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -20964,7 +21119,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -21035,7 +21190,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>0</v>
@@ -21106,7 +21261,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>0</v>
@@ -21177,7 +21332,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>0</v>
@@ -21248,7 +21403,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -21319,7 +21474,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -21390,7 +21545,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -21461,7 +21616,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -21532,7 +21687,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>0</v>
@@ -21603,7 +21758,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -21674,7 +21829,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -21745,7 +21900,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>0</v>
@@ -21816,7 +21971,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -21887,7 +22042,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -21958,7 +22113,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -22029,7 +22184,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -22100,7 +22255,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -22171,7 +22326,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>0</v>
@@ -22242,7 +22397,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -22313,7 +22468,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -22384,7 +22539,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>0</v>
@@ -22455,7 +22610,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>0</v>
@@ -22526,7 +22681,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>0</v>
@@ -22597,7 +22752,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>0</v>
@@ -22668,7 +22823,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -22739,7 +22894,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -22810,7 +22965,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -22881,7 +23036,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -22952,7 +23107,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>0</v>
@@ -23023,7 +23178,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -23094,7 +23249,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -23165,7 +23320,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -23236,7 +23391,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -23307,7 +23462,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>0</v>
@@ -23378,7 +23533,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>0</v>
@@ -23449,7 +23604,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>0</v>
@@ -23520,7 +23675,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -23591,7 +23746,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -23662,7 +23817,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -23733,7 +23888,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>0</v>
@@ -23804,7 +23959,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -23875,7 +24030,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>0</v>
@@ -23946,7 +24101,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -24017,7 +24172,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -24088,7 +24243,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -24159,7 +24314,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -24230,7 +24385,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -24301,7 +24456,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -24372,7 +24527,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -24443,7 +24598,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -24514,7 +24669,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -24585,7 +24740,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -24656,7 +24811,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>0</v>
@@ -24727,7 +24882,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -24798,7 +24953,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -24869,7 +25024,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -24940,7 +25095,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -25011,7 +25166,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -25082,7 +25237,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -25153,7 +25308,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -25224,7 +25379,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -25295,7 +25450,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -25366,7 +25521,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>0</v>
@@ -25437,7 +25592,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -25508,7 +25663,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -25579,7 +25734,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>0</v>
@@ -25650,7 +25805,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>0</v>
@@ -25721,7 +25876,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>0</v>
@@ -25792,7 +25947,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -25863,7 +26018,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -25934,7 +26089,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -26005,7 +26160,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -26076,7 +26231,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -26147,7 +26302,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -26218,7 +26373,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -26289,7 +26444,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -26360,7 +26515,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -26431,7 +26586,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="C350">
         <v>0</v>
@@ -26502,7 +26657,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C351">
         <v>0</v>
@@ -26573,7 +26728,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -26644,7 +26799,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -26715,7 +26870,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -26786,7 +26941,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -26857,7 +27012,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -26928,7 +27083,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C357">
         <v>0</v>
@@ -26999,7 +27154,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -27070,7 +27225,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -27141,7 +27296,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -27212,7 +27367,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C361">
         <v>0</v>
@@ -27283,7 +27438,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C362">
         <v>0</v>
@@ -27354,7 +27509,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C363">
         <v>0</v>
@@ -27425,7 +27580,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C364">
         <v>0</v>
@@ -27496,7 +27651,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C365">
         <v>0</v>
@@ -27567,7 +27722,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -27638,7 +27793,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -27709,7 +27864,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -27780,7 +27935,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -27851,7 +28006,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -27922,7 +28077,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -27993,7 +28148,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -28064,7 +28219,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -28135,7 +28290,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -28206,7 +28361,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -28277,7 +28432,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -28348,7 +28503,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -28419,7 +28574,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -28490,7 +28645,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -28561,7 +28716,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -28632,7 +28787,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C381">
         <v>0</v>
@@ -28703,7 +28858,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -28774,7 +28929,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -28845,7 +29000,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -28916,7 +29071,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -28987,7 +29142,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -29058,7 +29213,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -29129,7 +29284,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -29200,7 +29355,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -29271,7 +29426,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -29342,7 +29497,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -29413,7 +29568,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -29484,7 +29639,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -29555,7 +29710,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="C394">
         <v>0</v>
@@ -29626,7 +29781,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C395">
         <v>0</v>
@@ -29697,7 +29852,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C396">
         <v>0</v>
@@ -29768,7 +29923,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C397">
         <v>0</v>
@@ -29839,7 +29994,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="C398">
         <v>0</v>
@@ -29910,7 +30065,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C399">
         <v>0</v>
@@ -29981,7 +30136,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="C400">
         <v>0</v>
@@ -30052,7 +30207,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C401">
         <v>0</v>
@@ -30123,7 +30278,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -30194,7 +30349,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -30265,7 +30420,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C404">
         <v>0</v>
@@ -30336,7 +30491,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C405">
         <v>0</v>
@@ -30407,7 +30562,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C406">
         <v>0</v>
@@ -30478,7 +30633,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -30549,7 +30704,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="C408">
         <v>0</v>
@@ -30620,7 +30775,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="C409">
         <v>0</v>
@@ -30691,7 +30846,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C410">
         <v>0</v>
@@ -30762,7 +30917,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="C411">
         <v>0</v>
@@ -30833,7 +30988,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C412">
         <v>0</v>
@@ -30904,7 +31059,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="C413">
         <v>0</v>
@@ -30975,7 +31130,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C414">
         <v>0</v>
@@ -31046,7 +31201,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C415">
         <v>0</v>
@@ -31117,7 +31272,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="C416">
         <v>0</v>
@@ -31188,7 +31343,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C417">
         <v>0</v>
@@ -31259,7 +31414,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C418">
         <v>0</v>
@@ -31330,7 +31485,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -31401,7 +31556,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="C420">
         <v>0</v>
@@ -31472,7 +31627,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -31543,7 +31698,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C422">
         <v>0</v>
@@ -31614,7 +31769,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="C423">
         <v>0</v>
@@ -31685,7 +31840,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C424">
         <v>0</v>
@@ -31756,7 +31911,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C425">
         <v>0</v>
@@ -31827,7 +31982,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -31898,7 +32053,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C427">
         <v>0</v>
@@ -31969,7 +32124,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="C428">
         <v>0</v>
@@ -32040,7 +32195,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C429">
         <v>0</v>
@@ -32111,7 +32266,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C430">
         <v>0</v>
@@ -32182,7 +32337,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C431">
         <v>0</v>
@@ -32253,7 +32408,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="C432">
         <v>0</v>
@@ -32324,7 +32479,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C433">
         <v>0</v>
